--- a/financial_advisor_forms/023_financial_audit_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/023_financial_audit_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Advisor</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Contact Person Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Person Email</t>
+          <t>Contact Person Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact Person Phone</t>
+          <t>Company Name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Company Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Company Address</t>
+          <t>Financial Institution</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Company Location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,13 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Company Location</t>
+          <t>Financial Data Analysis Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,20 +824,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financial Data Analysis</t>
+          <t>Financial Audit Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Audit Date</t>
+          <t>Non-Compliance Issues</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auditing Process</t>
+          <t>Company Status</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,13 +893,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financial Advisor</t>
+          <t>Financial Audit Result</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Financial Data Collection</t>
+          <t>Financial Advisor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,149 +939,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Financial Audit Form 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>financial_audit_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Audit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>financial_audit_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Company Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>financial_audit_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Financial Audit Result</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>financial_audit_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Contact Person</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_audit_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Contact Person Phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>financial_audit_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Contact Person Email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +960,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1152,108 +1014,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>financial_audit_form_5_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>financial_audit_form_5_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>financial_audit_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>financial_audit_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>financial_audit_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>financial_audit_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
